--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EBB880-4DD2-4A19-99E0-DCB72B6CF2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D6281-B47E-471C-BADF-31EA9844AAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD2D6281-B47E-471C-BADF-31EA9844AAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF929853-E0D9-4331-8F45-10DA26ABC48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2370" yWindow="1980" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="185">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -637,10 +637,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>采集者会从攻防等级中获益，攻击等级+2采集量，防御等级-0.33采集时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>萨尔那加队长</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -677,10 +673,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>解锁宇宙要塞</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>单位受益于兵营（生命）、重工（能量）、星港（移动速度）能量场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -689,10 +681,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>防御建筑（地堡、补给站、导弹塔、要塞、侦测塔）减少50晶体矿消耗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>半完成</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -774,6 +762,22 @@
   </si>
   <si>
     <t>小队独特增益现在可以在Lawbda核心处对单位永久施加，花费对应单位的基础造价，冷却15秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>采集者会从攻防等级中获益，攻击等级+2采集量，防御等级-0.25采集时间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>完成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁宇宙要塞，防御建筑从军械库攻防中获益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御建筑（地堡、补给站、导弹塔、要塞、侦测塔）减少50晶体矿，50瓦斯消耗</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -797,12 +801,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -817,8 +827,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2113,66 +2124,66 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2">
+      <c r="A2" s="1">
         <f>ROW()-1</f>
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F2" t="s">
-        <v>62</v>
+      <c r="E2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="1">
         <f t="shared" ref="A3:A21" si="0">ROW()-1</f>
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" t="s">
-        <v>163</v>
+      <c r="E3" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <v>2</v>
       </c>
-      <c r="E4" t="s">
-        <v>149</v>
-      </c>
-      <c r="F4" t="s">
-        <v>62</v>
+      <c r="E4" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -2211,7 +2222,7 @@
         <v>3</v>
       </c>
       <c r="E6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F6" t="s">
         <v>62</v>
@@ -2223,7 +2234,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C7" t="s">
         <v>141</v>
@@ -2232,7 +2243,7 @@
         <v>3</v>
       </c>
       <c r="E7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F7" t="s">
         <v>62</v>
@@ -2244,7 +2255,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -2253,7 +2264,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -2265,7 +2276,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" t="s">
         <v>141</v>
@@ -2274,7 +2285,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -2286,7 +2297,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
         <v>141</v>
@@ -2295,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -2307,7 +2318,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -2316,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
@@ -2328,7 +2339,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C12" t="s">
         <v>142</v>
@@ -2337,7 +2348,7 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F12" t="s">
         <v>62</v>
@@ -2349,7 +2360,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C13" t="s">
         <v>142</v>
@@ -2358,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F13" t="s">
         <v>62</v>
@@ -2370,7 +2381,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C14" t="s">
         <v>142</v>
@@ -2379,7 +2390,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -2391,7 +2402,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C15" t="s">
         <v>142</v>
@@ -2400,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
@@ -2412,7 +2423,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -2421,7 +2432,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -2433,7 +2444,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C17" t="s">
         <v>142</v>
@@ -2442,7 +2453,7 @@
         <v>3</v>
       </c>
       <c r="E17" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F17" t="s">
         <v>62</v>
@@ -2454,7 +2465,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
         <v>142</v>
@@ -2463,7 +2474,7 @@
         <v>4</v>
       </c>
       <c r="E18" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -2475,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C19" t="s">
         <v>142</v>
@@ -2484,7 +2495,7 @@
         <v>4</v>
       </c>
       <c r="E19" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F19" t="s">
         <v>62</v>
@@ -2496,7 +2507,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C20" t="s">
         <v>142</v>
@@ -2505,7 +2516,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -2517,7 +2528,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C21" t="s">
         <v>142</v>
@@ -2526,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF929853-E0D9-4331-8F45-10DA26ABC48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42619EDE-1070-41FD-A5A7-E3194BD1C7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1980" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="186">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -629,10 +629,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>队员为采集者队长提供的经济效果提高25%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>武装采矿车</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -685,10 +681,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>初始1攻1防</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>先进军品</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -697,10 +689,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>攻防升级时间减少25%，解锁4级攻防</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>城市化建设</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -713,10 +701,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>增加资源恢复类技能效果（50%），允许采集者建造存量较少的矿脉和气泉作为回复目标</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>核弹天劫</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -729,10 +713,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>核弹消耗减少50瓦斯消耗，建造时间减半</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>超越光速</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -778,6 +758,30 @@
   </si>
   <si>
     <t>防御建筑（地堡、补给站、导弹塔、要塞、侦测塔）减少50晶体矿，50瓦斯消耗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>队员为采集者队长提供的经济效果提高25%（同样作用于指挥中心资源回复场）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核弹消耗减少50瓦斯消耗，建造时间减20s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>允许采集者建造采矿小屋，不影响单位采集矿脉，并且自动采集晶体矿，不会导致矿脉耗尽，可作为资源回复目标；解锁气矿自动采集能力，但是采集量较少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻防升级时间和消耗减少</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初始1攻1防，解锁4级攻防</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四级攻防不好做</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +805,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -811,6 +815,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,9 +837,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2096,14 +2107,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459D9287-1615-4311-B5EE-C74BA6AA5B09}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.75" customWidth="1"/>
-    <col min="5" max="5" width="87" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="102.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2123,7 +2134,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>ROW()-1</f>
         <v>1</v>
@@ -2138,13 +2149,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A21" si="0">ROW()-1</f>
         <v>2</v>
@@ -2159,19 +2170,19 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>141</v>
@@ -2180,82 +2191,82 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <v>2</v>
       </c>
-      <c r="E5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="E5" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <v>3</v>
       </c>
-      <c r="E6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="E6" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="C7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -2264,19 +2275,19 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9" t="s">
         <v>141</v>
@@ -2285,40 +2296,40 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="1">
+        <v>5</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C10" t="s">
-        <v>141</v>
-      </c>
-      <c r="D10">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
-        <v>152</v>
-      </c>
-      <c r="F10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" t="s">
         <v>141</v>
@@ -2327,61 +2338,64 @@
         <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F11" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
         <v>162</v>
-      </c>
-      <c r="C12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>164</v>
-      </c>
-      <c r="F13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>165</v>
       </c>
       <c r="C14" t="s">
         <v>142</v>
@@ -2390,19 +2404,19 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
         <v>142</v>
@@ -2411,19 +2425,19 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -2432,73 +2446,73 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17">
+      <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C17" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>172</v>
-      </c>
-      <c r="F17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>173</v>
-      </c>
-      <c r="C18" t="s">
-        <v>142</v>
-      </c>
-      <c r="D18">
-        <v>4</v>
-      </c>
-      <c r="E18" t="s">
-        <v>174</v>
-      </c>
-      <c r="F18" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" t="s">
-        <v>142</v>
-      </c>
-      <c r="D19">
-        <v>4</v>
-      </c>
-      <c r="E19" t="s">
-        <v>176</v>
-      </c>
-      <c r="F19" t="s">
-        <v>62</v>
+      <c r="F19" s="1" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -2507,7 +2521,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C20" t="s">
         <v>142</v>
@@ -2516,7 +2530,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -2528,7 +2542,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C21" t="s">
         <v>142</v>
@@ -2537,7 +2551,7 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42619EDE-1070-41FD-A5A7-E3194BD1C7F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC36C4B0-F6C4-4F94-8804-46F580C3C1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="960" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>
@@ -2345,23 +2345,23 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
+      <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>1</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="1" t="s">
         <v>159</v>
       </c>
       <c r="G12" s="2" t="s">

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC36C4B0-F6C4-4F94-8804-46F580C3C1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3923809A-3C1B-464F-8E43-5B4C3D098637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6180" yWindow="960" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="185">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -637,10 +637,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>队长单位现在可以获得经验升级，每级提高25%生命和攻击力，但无法解散小队</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>额外补给</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -677,10 +673,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>半完成</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>先进军品</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -782,6 +774,10 @@
   </si>
   <si>
     <t>四级攻防不好做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>队长单位现在可以获得经验升级，每级提高25%生命和攻击力（最高3级），但无法解散小队</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2149,10 +2145,10 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -2170,10 +2166,10 @@
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -2191,10 +2187,10 @@
         <v>2</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -2212,10 +2208,10 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -2233,10 +2229,10 @@
         <v>3</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -2245,7 +2241,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>141</v>
@@ -2254,10 +2250,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -2266,7 +2262,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" t="s">
         <v>141</v>
@@ -2275,7 +2271,7 @@
         <v>4</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F8" t="s">
         <v>62</v>
@@ -2287,7 +2283,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C9" t="s">
         <v>141</v>
@@ -2296,7 +2292,7 @@
         <v>4</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -2308,7 +2304,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>141</v>
@@ -2317,31 +2313,31 @@
         <v>5</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="1">
         <v>5</v>
       </c>
-      <c r="E11" t="s">
-        <v>149</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
+      <c r="E11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -2350,7 +2346,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>142</v>
@@ -2359,13 +2355,13 @@
         <v>1</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -2374,7 +2370,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>142</v>
@@ -2383,10 +2379,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -2395,7 +2391,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
         <v>142</v>
@@ -2404,7 +2400,7 @@
         <v>2</v>
       </c>
       <c r="E14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -2416,7 +2412,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C15" t="s">
         <v>142</v>
@@ -2425,7 +2421,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F15" t="s">
         <v>62</v>
@@ -2437,7 +2433,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C16" t="s">
         <v>142</v>
@@ -2446,7 +2442,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F16" t="s">
         <v>62</v>
@@ -2458,7 +2454,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>142</v>
@@ -2467,10 +2463,10 @@
         <v>3</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -2479,7 +2475,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>142</v>
@@ -2488,10 +2484,10 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -2500,7 +2496,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>142</v>
@@ -2509,10 +2505,10 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -2521,7 +2517,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C20" t="s">
         <v>142</v>
@@ -2530,7 +2526,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F20" t="s">
         <v>62</v>
@@ -2542,7 +2538,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C21" t="s">
         <v>142</v>
@@ -2551,7 +2547,7 @@
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F21" t="s">
         <v>62</v>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3923809A-3C1B-464F-8E43-5B4C3D098637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1815262-467B-458D-AF24-B0B3317C17FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="960" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -778,6 +778,10 @@
   </si>
   <si>
     <t>队长单位现在可以获得经验升级，每级提高25%生命和攻击力（最高3级），但无法解散小队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>改为采矿小屋（但是有bug，建筑足印问题）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2108,6 +2112,7 @@
   <cols>
     <col min="2" max="2" width="25.75" customWidth="1"/>
     <col min="5" max="5" width="102.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -2386,45 +2391,48 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14">
+      <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="1">
         <v>2</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F14" t="s">
-        <v>62</v>
+      <c r="F14" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15">
+      <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="1">
         <v>2</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F15" t="s">
-        <v>62</v>
+      <c r="F15" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1815262-467B-458D-AF24-B0B3317C17FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535170DF-142D-4C07-A631-7166BEF5D1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="189">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -782,6 +782,18 @@
   </si>
   <si>
     <t>改为采矿小屋（但是有bug，建筑足印问题）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>废案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄升级增益提高50%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>英雄升级经验减33%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2107,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{459D9287-1615-4311-B5EE-C74BA6AA5B09}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="25.75" customWidth="1"/>
@@ -2115,7 +2127,7 @@
     <col min="7" max="7" width="41.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2134,8 +2146,11 @@
       <c r="F1" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <f>ROW()-1</f>
         <v>1</v>
@@ -2156,7 +2171,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <f t="shared" ref="A3:A21" si="0">ROW()-1</f>
         <v>2</v>
@@ -2177,7 +2192,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2198,7 +2213,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2219,7 +2234,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2240,7 +2255,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2261,49 +2276,55 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="1">
         <v>4</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H8" t="s">
         <v>153</v>
       </c>
-      <c r="F8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="1">
         <v>4</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H9" t="s">
         <v>154</v>
       </c>
-      <c r="F9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2324,7 +2345,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2345,7 +2366,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2369,7 +2390,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2390,7 +2411,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2411,7 +2432,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2435,7 +2456,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{535170DF-142D-4C07-A631-7166BEF5D1D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F033527-B05E-4079-8509-16B02A3F781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2541,44 +2541,44 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20">
+      <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="1">
         <v>5</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21">
+      <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="1">
         <v>5</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="1" t="s">
         <v>62</v>
       </c>
     </row>

--- a/doc/军械库和实验室科技.xlsx
+++ b/doc/军械库和实验室科技.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lawbda\Desktop\Github\Wings-of-Combination\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F033527-B05E-4079-8509-16B02A3F781A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DB02E9-A123-440C-AC67-68557BEFAFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="军械库" sheetId="1" r:id="rId1"/>
@@ -2457,24 +2457,24 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16">
+      <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F16" t="s">
-        <v>62</v>
+      <c r="F16" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -2558,7 +2558,7 @@
         <v>171</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -2579,7 +2579,7 @@
         <v>173</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
